--- a/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,94 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Notification Setting</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KGF6VEY028ED2AR4GQJQKE7F</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGF6VEY028ED2AR4GQJQKE7F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,6 +768,72 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Scenario - in UI keep it first</t>
+          <t>Integration Scenario</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">

--- a/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KHJWBXCD7MDNEET5RDNSBTNR</t>
+          <t>h_01KHTXB9DM26403EVHMYTAA9EB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KHJWBXCD7MDNEET5RDNSBTNR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KHTXB9DM26403EVHMYTAA9EB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01KHJWBXCD7MDNEET5RDNSBTNR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KHJWBXCD7MDNEET5RDNSBTNR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,41 +539,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,41 +583,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>h_01K3TMW0YGBNCAV57V69WX0VWV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K3TMW0YGBNCAV57V69WX0VWV</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integration Scenario</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Integration Scenario</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>User Management</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGHCM05P16HDNGNGD0D9R5CG</t>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHCM05P16HDNGNGD0D9R5CG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>h_01KGHCM05P16HDNGNGD0D9R5CG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHCM05P16HDNGNGD0D9R5CG</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
+          <t>h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH3ZZ8TA8NBG5BHDVSRZBB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHFT7BX2WGGEDSQZ75MJ1TQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification Setting</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,76 +759,98 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGF6VEY028ED2AR4GQJQKE7F</t>
+          <t>h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGF6VEY028ED2AR4GQJQKE7F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGHH5EYXPD55T3QNB33EB738</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGF6VEY028ED2AR4GQJQKE7F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01KGF6VEY028ED2AR4GQJQKE7F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Oracle-Identity-Manager-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Oracle-Identity-Manager-Integration-Guide/headings.xlsx
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Setting</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
